--- a/sample_students.xlsx
+++ b/sample_students.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="69">
   <si>
     <t>Student</t>
   </si>
@@ -178,40 +178,49 @@
     <t>Student_050</t>
   </si>
   <si>
+    <t>Life Science and Technology</t>
+  </si>
+  <si>
     <t>Maritieme Techniek</t>
   </si>
   <si>
+    <t>Klinische Technologie</t>
+  </si>
+  <si>
+    <t>Molecular Science and Technology</t>
+  </si>
+  <si>
+    <t>Aerospace Engineering</t>
+  </si>
+  <si>
+    <t>Technische Natuurkunde</t>
+  </si>
+  <si>
+    <t>Werktuigbouwkunde</t>
+  </si>
+  <si>
     <t>Industrieel Ontwerpen</t>
   </si>
   <si>
-    <t>Technische Natuurkunde</t>
-  </si>
-  <si>
-    <t>Werktuigbouwkunde</t>
+    <t>Earth, Climate and Technology</t>
   </si>
   <si>
     <t>Civiele Techniek</t>
   </si>
   <si>
+    <t>Computer Science and Engineering</t>
+  </si>
+  <si>
+    <t>Bouwkunde</t>
+  </si>
+  <si>
+    <t>Electrical Engineering</t>
+  </si>
+  <si>
+    <t>Nanobiology</t>
+  </si>
+  <si>
     <t>Technische Bestuurskunde</t>
-  </si>
-  <si>
-    <t>Bouwkunde</t>
-  </si>
-  <si>
-    <t>Electrical Engineering</t>
-  </si>
-  <si>
-    <t>Aerospace Engineering</t>
-  </si>
-  <si>
-    <t>Life Science and Technology</t>
-  </si>
-  <si>
-    <t>Klinische Technologie</t>
-  </si>
-  <si>
-    <t>Computer Science and Engineering</t>
   </si>
 </sst>
 </file>
@@ -568,10 +577,10 @@
         <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -582,10 +591,10 @@
         <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -599,7 +608,7 @@
         <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -610,10 +619,10 @@
         <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -621,13 +630,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -635,13 +644,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
         <v>60</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -649,13 +658,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -663,13 +672,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -677,13 +686,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -691,13 +700,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -705,13 +714,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -719,7 +728,7 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
         <v>65</v>
@@ -733,13 +742,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
         <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -747,13 +756,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -761,13 +770,13 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -775,13 +784,13 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D17" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -789,13 +798,13 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -803,13 +812,13 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -817,13 +826,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -831,13 +840,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -845,13 +854,13 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -859,13 +868,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -873,13 +882,13 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -887,13 +896,13 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -901,13 +910,13 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -918,10 +927,10 @@
         <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D27" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -929,13 +938,13 @@
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -943,13 +952,13 @@
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -957,13 +966,13 @@
         <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D30" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -971,13 +980,13 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -985,13 +994,13 @@
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D32" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -999,13 +1008,13 @@
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D33" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1013,13 +1022,13 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="D34" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1027,13 +1036,13 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D35" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1041,13 +1050,13 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D36" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1055,13 +1064,13 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1069,13 +1078,13 @@
         <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D38" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1083,13 +1092,13 @@
         <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D39" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1097,13 +1106,13 @@
         <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D40" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1111,13 +1120,13 @@
         <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C41" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D41" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1125,13 +1134,13 @@
         <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D42" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1139,10 +1148,10 @@
         <v>45</v>
       </c>
       <c r="B43" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" t="s">
         <v>61</v>
-      </c>
-      <c r="C43" t="s">
-        <v>65</v>
       </c>
       <c r="D43" t="s">
         <v>57</v>
@@ -1153,13 +1162,13 @@
         <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C44" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1167,13 +1176,13 @@
         <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C45" t="s">
         <v>58</v>
       </c>
       <c r="D45" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1181,13 +1190,13 @@
         <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D46" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1195,13 +1204,13 @@
         <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D47" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1209,13 +1218,13 @@
         <v>50</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C48" t="s">
         <v>61</v>
       </c>
       <c r="D48" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1223,13 +1232,13 @@
         <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D49" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1237,10 +1246,10 @@
         <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C50" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D50" t="s">
         <v>58</v>
@@ -1251,13 +1260,13 @@
         <v>53</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D51" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
